--- a/Data/A1_DataFromAutoExtraction_PreManualExtraction/Topics_ExtractedBinary_PosthocRd2.xlsx
+++ b/Data/A1_DataFromAutoExtraction_PreManualExtraction/Topics_ExtractedBinary_PosthocRd2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritwikavps/Desktop/GoogleDriveFiles/research/DARCLEPaper2025/DARCLEPaper2025_ExtractionCode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritwikavps/Desktop/GoogleDriveFiles/research/DARCLEPaper2025/DARCLEPaper2025_ExtractionCode/Data/A1_DataFromAutoExtraction_PreManualExtraction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED641F2A-98D8-2943-9D7D-48A482ED8C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D238C47D-9ED6-694A-B91C-392641BF1F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5600" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
   <si>
     <t>PaperTitle_ToC</t>
   </si>
@@ -59,15 +59,6 @@
   </si>
   <si>
     <t>NICU</t>
-  </si>
-  <si>
-    <t>Language outcomes and service provision of preschool children with congenital hearing loss</t>
-  </si>
-  <si>
-    <t>Early Human  Development</t>
-  </si>
-  <si>
-    <t>1-s2.0-S037837821100377X-main</t>
   </si>
   <si>
     <t>NO</t>
@@ -461,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="44.6640625" style="2" customWidth="1"/>
@@ -519,86 +510,86 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
+    <row r="2" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="80" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
@@ -606,75 +597,34 @@
         <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
